--- a/ranking personalizowany.xlsx
+++ b/ranking personalizowany.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mati\Documents\Magisterka\Magisterka\Praca magisterska\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A9859A-8C09-4CE2-BE16-8348079B22C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD39E238-63B4-4B7F-B497-7A6AC96C59EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16896" firstSheet="1" activeTab="9" xr2:uid="{0B950873-47D3-498D-8B2A-DE09D96574AA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="16680" firstSheet="8" activeTab="10" xr2:uid="{0B950873-47D3-498D-8B2A-DE09D96574AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Zabytki i kultura" sheetId="8" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="621">
   <si>
     <t>Francja</t>
   </si>
@@ -1870,19 +1870,10 @@
     <t>Safety and Security pillar (WEF)</t>
   </si>
   <si>
-    <t>49.8</t>
-  </si>
-  <si>
     <t>Nazwa kraju SIDS</t>
   </si>
   <si>
     <t>Jamajka</t>
-  </si>
-  <si>
-    <t>55.3</t>
-  </si>
-  <si>
-    <t>32.6</t>
   </si>
   <si>
     <t>Safety Index (Numbeo)</t>
@@ -5623,7 +5614,7 @@
         <f>($E$63-E2)/($E$63-$E$62)</f>
         <v>0.98229355423246179</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <f>($F$63-F2)/($F$63-$F$62)</f>
         <v>0.29069767441860461</v>
       </c>
@@ -5669,7 +5660,7 @@
         <f t="shared" ref="G3:G61" si="1">($E$63-E3)/($E$63-$E$62)</f>
         <v>0.97908361377167996</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <f t="shared" ref="H3:H61" si="2">($F$63-F3)/($F$63-$F$62)</f>
         <v>0.52470930232558133</v>
       </c>
@@ -5715,7 +5706,7 @@
         <f t="shared" si="1"/>
         <v>0.60559150918974891</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <f t="shared" si="2"/>
         <v>0.27470930232558144</v>
       </c>
@@ -5761,7 +5752,7 @@
         <f t="shared" si="1"/>
         <v>0.94061610147553709</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <f t="shared" si="2"/>
         <v>0.7049418604651162</v>
       </c>
@@ -5807,7 +5798,7 @@
         <f t="shared" si="1"/>
         <v>0.99647942013978763</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <f t="shared" si="2"/>
         <v>0.38226744186046513</v>
       </c>
@@ -5853,7 +5844,7 @@
         <f t="shared" si="1"/>
         <v>0.54869272586073004</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <f t="shared" si="2"/>
         <v>0.65552325581395343</v>
       </c>
@@ -5899,7 +5890,7 @@
         <f t="shared" si="1"/>
         <v>0.99446026404348942</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <f t="shared" si="2"/>
         <v>0.28924418604651164</v>
       </c>
@@ -5945,7 +5936,7 @@
         <f t="shared" si="1"/>
         <v>0.50577271550608338</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <f t="shared" si="2"/>
         <v>0.58430232558139528</v>
       </c>
@@ -5991,7 +5982,7 @@
         <f t="shared" si="1"/>
         <v>0.98011907843644841</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="27">
         <f t="shared" si="2"/>
         <v>0.48982558139534882</v>
       </c>
@@ -6037,7 +6028,7 @@
         <f t="shared" si="1"/>
         <v>0.62795754594874453</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <f t="shared" si="2"/>
         <v>0.72238372093023251</v>
       </c>
@@ -6083,7 +6074,7 @@
         <f t="shared" si="1"/>
         <v>0.98560704115972042</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="27">
         <f t="shared" si="2"/>
         <v>0.23837209302325585</v>
       </c>
@@ -6129,7 +6120,7 @@
         <f t="shared" si="1"/>
         <v>0.95645871084649225</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="27">
         <f t="shared" si="2"/>
         <v>0.56540697674418605</v>
       </c>
@@ -6177,7 +6168,7 @@
         <f t="shared" si="1"/>
         <v>0.58700491845715763</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="27">
         <f t="shared" si="2"/>
         <v>0.78052325581395343</v>
       </c>
@@ -6190,7 +6181,7 @@
         <v>0.69001978825878074</v>
       </c>
       <c r="L14" s="92" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M14" s="93"/>
       <c r="N14" s="94"/>
@@ -6219,7 +6210,7 @@
         <f t="shared" si="1"/>
         <v>0.59461558374320478</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="27">
         <f t="shared" si="2"/>
         <v>0.83139534883720922</v>
       </c>
@@ -6256,7 +6247,7 @@
         <f t="shared" si="1"/>
         <v>0.98721201139011117</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="27">
         <f t="shared" si="2"/>
         <v>0.20784883720930225</v>
       </c>
@@ -6293,7 +6284,7 @@
         <f t="shared" si="1"/>
         <v>0.70121667098110274</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="27">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -6330,7 +6321,7 @@
         <f t="shared" si="1"/>
         <v>0.66580377944602642</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <f t="shared" si="2"/>
         <v>0.35901162790697672</v>
       </c>
@@ -6367,7 +6358,7 @@
         <f t="shared" si="1"/>
         <v>0.57494175511260681</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="27">
         <f t="shared" si="2"/>
         <v>0.89098837209302317</v>
       </c>
@@ -6404,7 +6395,7 @@
         <f t="shared" si="1"/>
         <v>0.95759772197773751</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="27">
         <f t="shared" si="2"/>
         <v>0.81831395348837199</v>
       </c>
@@ -6441,8 +6432,8 @@
         <f t="shared" si="1"/>
         <v>0.92373802743981359</v>
       </c>
-      <c r="H21" s="28">
-        <f t="shared" si="2"/>
+      <c r="H21" s="27">
+        <f>($F$63-F21)/($F$63-$F$62)</f>
         <v>0.96075581395348808</v>
       </c>
       <c r="I21" s="27">
@@ -6478,7 +6469,7 @@
         <f t="shared" si="1"/>
         <v>0.55625161791353872</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="27">
         <f t="shared" si="2"/>
         <v>0.89534883720930225</v>
       </c>
@@ -6515,7 +6506,7 @@
         <f t="shared" si="1"/>
         <v>0.99347657261195965</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="27">
         <f t="shared" si="2"/>
         <v>0.59302325581395343</v>
       </c>
@@ -6552,7 +6543,7 @@
         <f t="shared" si="1"/>
         <v>0.60626456122184824</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6589,7 +6580,7 @@
         <f t="shared" si="1"/>
         <v>0.96966088532228834</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="27">
         <f t="shared" si="2"/>
         <v>0.60901162790697672</v>
       </c>
@@ -6626,7 +6617,7 @@
         <f t="shared" si="1"/>
         <v>0.7782552420398654</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="27">
         <f t="shared" si="2"/>
         <v>0.84156976744186041</v>
       </c>
@@ -6663,7 +6654,7 @@
         <f t="shared" si="1"/>
         <v>0.88713435154025366</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="27">
         <f t="shared" si="2"/>
         <v>0.85174418604651148</v>
       </c>
@@ -6700,7 +6691,7 @@
         <f t="shared" si="1"/>
         <v>0.63650012943308298</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="27">
         <f t="shared" si="2"/>
         <v>0.73546511627906963</v>
       </c>
@@ -6737,7 +6728,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="27">
         <f t="shared" si="2"/>
         <v>0.28633720930232559</v>
       </c>
@@ -6774,7 +6765,7 @@
         <f t="shared" si="1"/>
         <v>0.99611700750711885</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="27">
         <f t="shared" si="2"/>
         <v>0.67005813953488358</v>
       </c>
@@ -6811,7 +6802,7 @@
         <f t="shared" si="1"/>
         <v>0.50038829924928807</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="27">
         <f t="shared" si="2"/>
         <v>0.71947674418604635</v>
       </c>
@@ -6848,7 +6839,7 @@
         <f t="shared" si="1"/>
         <v>0.39968936060056948</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="27">
         <f t="shared" si="2"/>
         <v>0.28779069767441851</v>
       </c>
@@ -6885,7 +6876,7 @@
         <f t="shared" si="1"/>
         <v>0.77804814910691178</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="27">
         <f t="shared" si="2"/>
         <v>0.87790697674418594</v>
       </c>
@@ -6922,7 +6913,7 @@
         <f t="shared" si="1"/>
         <v>0.48356199844680298</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="27">
         <f t="shared" si="2"/>
         <v>0.83720930232558133</v>
       </c>
@@ -6959,7 +6950,7 @@
         <f t="shared" si="1"/>
         <v>0.44478384675122962</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="27">
         <f t="shared" si="2"/>
         <v>0.81395348837209291</v>
       </c>
@@ -6996,7 +6987,7 @@
         <f t="shared" si="1"/>
         <v>0.52720683406678748</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="27">
         <f t="shared" si="2"/>
         <v>0.76889534883720922</v>
       </c>
@@ -7033,7 +7024,7 @@
         <f t="shared" si="1"/>
         <v>0.37592544654413673</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="27">
         <f t="shared" si="2"/>
         <v>0.67441860465116277</v>
       </c>
@@ -7070,7 +7061,7 @@
         <f t="shared" si="1"/>
         <v>0.96184312710328757</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="27">
         <f t="shared" si="2"/>
         <v>0.24854651162790706</v>
       </c>
@@ -7107,7 +7098,7 @@
         <f t="shared" si="1"/>
         <v>0.55889205280869791</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="27">
         <f t="shared" si="2"/>
         <v>0.83720930232558133</v>
       </c>
@@ -7144,7 +7135,7 @@
         <f t="shared" si="1"/>
         <v>0.47186124773492105</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="27">
         <f t="shared" si="2"/>
         <v>0.36482558139534882</v>
       </c>
@@ -7181,7 +7172,7 @@
         <f t="shared" si="1"/>
         <v>0.38902407455345589</v>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="27">
         <f t="shared" si="2"/>
         <v>0.70784883720930225</v>
       </c>
@@ -7218,7 +7209,7 @@
         <f t="shared" si="1"/>
         <v>0.9666062645612219</v>
       </c>
-      <c r="H42" s="28">
+      <c r="H42" s="27">
         <f t="shared" si="2"/>
         <v>0.79360465116279055</v>
       </c>
@@ -7255,7 +7246,7 @@
         <f t="shared" si="1"/>
         <v>0.97763396324100438</v>
       </c>
-      <c r="H43" s="28">
+      <c r="H43" s="27">
         <f t="shared" si="2"/>
         <v>0.47383720930232553</v>
       </c>
@@ -7292,7 +7283,7 @@
         <f t="shared" si="1"/>
         <v>0.9709034429200103</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H44" s="27">
         <f t="shared" si="2"/>
         <v>0.42005813953488375</v>
       </c>
@@ -7329,7 +7320,7 @@
         <f t="shared" si="1"/>
         <v>0.62707740098369136</v>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="27">
         <f t="shared" si="2"/>
         <v>0.78197674418604646</v>
       </c>
@@ -7366,7 +7357,7 @@
         <f t="shared" si="1"/>
         <v>0.18633186642505828</v>
       </c>
-      <c r="H46" s="28">
+      <c r="H46" s="27">
         <f t="shared" si="2"/>
         <v>0.39825581395348841</v>
       </c>
@@ -7403,7 +7394,7 @@
         <f t="shared" si="1"/>
         <v>0.50541030287341449</v>
       </c>
-      <c r="H47" s="28">
+      <c r="H47" s="27">
         <f t="shared" si="2"/>
         <v>0.91133720930232542</v>
       </c>
@@ -7440,7 +7431,7 @@
         <f t="shared" si="1"/>
         <v>3.5775304167745367E-2</v>
       </c>
-      <c r="H48" s="28">
+      <c r="H48" s="27">
         <f t="shared" si="2"/>
         <v>0.77616279069767435</v>
       </c>
@@ -7477,7 +7468,7 @@
         <f t="shared" si="1"/>
         <v>0.99440849081025107</v>
       </c>
-      <c r="H49" s="28">
+      <c r="H49" s="27">
         <f t="shared" si="2"/>
         <v>0.27180232558139533</v>
       </c>
@@ -7514,7 +7505,7 @@
         <f t="shared" si="1"/>
         <v>0.53145223919233753</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="27">
         <f t="shared" si="2"/>
         <v>0.37936046511627902</v>
       </c>
@@ -7551,7 +7542,7 @@
         <f t="shared" si="1"/>
         <v>0.93828630597980833</v>
       </c>
-      <c r="H51" s="28">
+      <c r="H51" s="27">
         <f t="shared" si="2"/>
         <v>0.71220930232558133</v>
       </c>
@@ -7588,7 +7579,7 @@
         <f t="shared" si="1"/>
         <v>0.97986021227025621</v>
       </c>
-      <c r="H52" s="28">
+      <c r="H52" s="27">
         <f t="shared" si="2"/>
         <v>0.50436046511627908</v>
       </c>
@@ -7625,7 +7616,7 @@
         <f t="shared" si="1"/>
         <v>0.5741133833807921</v>
       </c>
-      <c r="H53" s="28">
+      <c r="H53" s="27">
         <f t="shared" si="2"/>
         <v>0.56395348837209303</v>
       </c>
@@ -7662,7 +7653,7 @@
         <f t="shared" si="1"/>
         <v>0.44147035982397098</v>
       </c>
-      <c r="H54" s="28">
+      <c r="H54" s="27">
         <f t="shared" si="2"/>
         <v>0.6875</v>
       </c>
@@ -7699,7 +7690,7 @@
         <f t="shared" si="1"/>
         <v>0.91752523945120379</v>
       </c>
-      <c r="H55" s="28">
+      <c r="H55" s="27">
         <f t="shared" si="2"/>
         <v>0.48837209302325574</v>
       </c>
@@ -7736,7 +7727,7 @@
         <f t="shared" si="1"/>
         <v>0.37525239451203724</v>
       </c>
-      <c r="H56" s="28">
+      <c r="H56" s="27">
         <f t="shared" si="2"/>
         <v>0.78779069767441856</v>
       </c>
@@ -7773,7 +7764,7 @@
         <f t="shared" si="1"/>
         <v>0.5664509448615066</v>
       </c>
-      <c r="H57" s="28">
+      <c r="H57" s="27">
         <f t="shared" si="2"/>
         <v>0.88808139534883712</v>
       </c>
@@ -7811,7 +7802,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H58" s="28">
+      <c r="H58" s="27">
         <f t="shared" si="2"/>
         <v>0.27897784245479706</v>
       </c>
@@ -7848,7 +7839,7 @@
         <f t="shared" si="1"/>
         <v>0.56795236862542064</v>
       </c>
-      <c r="H59" s="28">
+      <c r="H59" s="27">
         <f t="shared" si="2"/>
         <v>0.33720930232558138</v>
       </c>
@@ -7885,7 +7876,7 @@
         <f t="shared" si="1"/>
         <v>0.97307791871602367</v>
       </c>
-      <c r="H60" s="28">
+      <c r="H60" s="27">
         <f t="shared" si="2"/>
         <v>0.44912790697674421</v>
       </c>
@@ -7922,7 +7913,7 @@
         <f t="shared" si="1"/>
         <v>0.96639917162826805</v>
       </c>
-      <c r="H61" s="28">
+      <c r="H61" s="27">
         <f t="shared" si="2"/>
         <v>0.51308139534883723</v>
       </c>
@@ -8001,16 +7992,16 @@
         <v>606</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>611</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>612</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>614</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>615</v>
-      </c>
       <c r="F1" s="23" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G1" s="23" t="s">
         <v>579</v>
@@ -9568,7 +9559,7 @@
       </c>
       <c r="C59" s="11">
         <f>B70</f>
-        <v>40</v>
+        <v>44.424999999999997</v>
       </c>
       <c r="D59" s="27">
         <f t="shared" si="0"/>
@@ -9576,15 +9567,15 @@
       </c>
       <c r="E59" s="27">
         <f t="shared" si="1"/>
-        <v>0.47169811320754718</v>
+        <v>0.523879716981132</v>
       </c>
       <c r="F59" s="27">
         <f t="shared" si="2"/>
-        <v>0.61338067389782025</v>
+        <v>0.63947147578461261</v>
       </c>
       <c r="G59" s="26">
         <f t="shared" si="3"/>
-        <v>0.33287296794132321</v>
+        <v>0.38353376784035315</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -9669,18 +9660,18 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="B66" s="53" t="s">
-        <v>607</v>
+      <c r="B66" s="53">
+        <v>49.8</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -9695,25 +9686,25 @@
       <c r="A68" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="B68" s="53" t="s">
-        <v>610</v>
+      <c r="B68" s="53">
+        <v>55.3</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="B69" s="53" t="s">
-        <v>611</v>
+        <v>608</v>
+      </c>
+      <c r="B69" s="53">
+        <v>32.6</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="49" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B70" s="76">
         <f>AVERAGE(B66:B69)</f>
-        <v>40</v>
+        <v>44.424999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -9740,22 +9731,22 @@
         <v>67</v>
       </c>
       <c r="B1" s="23" t="s">
+        <v>614</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>616</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>617</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="F1" s="23" t="s">
         <v>618</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="G1" s="23" t="s">
         <v>619</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>620</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>621</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">

--- a/ranking personalizowany.xlsx
+++ b/ranking personalizowany.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mati\Documents\Magisterka\Magisterka\Praca magisterska\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD39E238-63B4-4B7F-B497-7A6AC96C59EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB17207-A5B3-42B7-95C6-8937416BA048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="16680" firstSheet="8" activeTab="10" xr2:uid="{0B950873-47D3-498D-8B2A-DE09D96574AA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="16680" firstSheet="8" activeTab="11" xr2:uid="{0B950873-47D3-498D-8B2A-DE09D96574AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Zabytki i kultura" sheetId="8" r:id="rId1"/>
@@ -11080,7 +11080,7 @@
         <v>0.53348985323578613</v>
       </c>
       <c r="G59" s="27">
-        <v>0.33287296794132321</v>
+        <v>0.38353376784035315</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
